--- a/data/trans_dic/IP16A07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A07-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir</t>
+          <t>Menores que consumiero pastillas para dormir (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,37</t>
+          <t>0,0; 6,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 9,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,62</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,71</t>
+          <t>0,0; 11,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,29</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,48</t>
+          <t>0,31; 3,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,8</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero pastillas para dormir (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3597</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4626</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3025</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4311</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4205</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3282</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>545; 6682</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3937</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>576; 5737</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A07-Edad-trans_dic.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,7</t>
+          <t>0,0; 6,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>0,0; 8,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 5,36</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,22</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,76</t>
+          <t>0,28; 3,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,15; 1,58</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3597</t>
+          <t>0; 3294</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4626</t>
+          <t>0; 4152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3025</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4311</t>
+          <t>0; 5127</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>0; 3762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4205</t>
+          <t>0; 3879</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3282</t>
+          <t>0; 3768</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>545; 6682</t>
+          <t>497; 5750</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 3937</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>576; 5737</t>
+          <t>555; 5688</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A07-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron pastillas para dormir (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -794,29 +794,29 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 5,68</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1214,29 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,37; 4,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,58</t>
+          <t>0,18; 2,1</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron pastillas para dormir (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1790,29 +1790,29 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1194</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3294</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4152</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3956</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3925</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 3992</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5127</t>
+          <t>0; 4129</t>
         </is>
       </c>
     </row>
@@ -1940,27 +1940,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>867</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>867</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3762</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4221</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3879</t>
+          <t>0; 4652</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2414,29 +2414,29 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2061</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3768</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>497; 5750</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3255</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>528; 6121</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 3038</t>
+          <t>0; 3462</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>555; 5688</t>
+          <t>549; 6470</t>
         </is>
       </c>
     </row>
